--- a/research/traditional_assets/database/data/finland/finland_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.144</v>
+        <v>0.059</v>
       </c>
       <c r="E2">
-        <v>-0.142</v>
+        <v>-0.011</v>
       </c>
       <c r="F2">
-        <v>1.221</v>
+        <v>-0.136</v>
       </c>
       <c r="G2">
-        <v>0.01707948725368211</v>
+        <v>0.3609605769331558</v>
       </c>
       <c r="H2">
-        <v>0.01707948725368211</v>
+        <v>0.3609605769331558</v>
       </c>
       <c r="I2">
-        <v>0.07847449289620648</v>
+        <v>0.2835819331034266</v>
       </c>
       <c r="J2">
-        <v>0.05390661720818591</v>
+        <v>0.2447875084196423</v>
       </c>
       <c r="K2">
-        <v>831</v>
+        <v>2176.9</v>
       </c>
       <c r="L2">
-        <v>0.06011458664891924</v>
+        <v>0.2281841909413947</v>
       </c>
       <c r="M2">
-        <v>1094.1</v>
+        <v>3561.5</v>
       </c>
       <c r="N2">
-        <v>0.04009337163964703</v>
+        <v>0.13269028005976</v>
       </c>
       <c r="O2">
-        <v>1.316606498194946</v>
+        <v>1.636042078184574</v>
       </c>
       <c r="P2">
-        <v>1094.1</v>
+        <v>2143.6</v>
       </c>
       <c r="Q2">
-        <v>0.04009337163964703</v>
+        <v>0.07986378894738214</v>
       </c>
       <c r="R2">
-        <v>1.316606498194946</v>
+        <v>0.9847030180531948</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1417.9</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.3981187701811035</v>
       </c>
       <c r="U2">
-        <v>5003.5</v>
+        <v>2635.8</v>
       </c>
       <c r="V2">
-        <v>0.1833536102723462</v>
+        <v>0.09820161173143771</v>
       </c>
       <c r="W2">
-        <v>0.06048563193291991</v>
+        <v>0.1508865076174501</v>
       </c>
       <c r="X2">
-        <v>0.05151743282074887</v>
+        <v>0.08331591340791074</v>
       </c>
       <c r="Y2">
-        <v>0.008968199112171039</v>
+        <v>0.06757059420953941</v>
       </c>
       <c r="Z2">
-        <v>0.7481072188157875</v>
+        <v>0.6487921982535839</v>
       </c>
       <c r="AA2">
-        <v>0.04032792947538323</v>
+        <v>0.1588162256925974</v>
       </c>
       <c r="AB2">
-        <v>0.04703746789792786</v>
+        <v>0.07915047207117519</v>
       </c>
       <c r="AC2">
-        <v>-0.006709538422544625</v>
+        <v>0.07966575362142224</v>
       </c>
       <c r="AD2">
-        <v>5280.5</v>
+        <v>3404.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5280.5</v>
+        <v>3404.6</v>
       </c>
       <c r="AG2">
-        <v>277</v>
+        <v>768.7999999999997</v>
       </c>
       <c r="AH2">
-        <v>0.1621312094518458</v>
+        <v>0.1125662499628041</v>
       </c>
       <c r="AI2">
-        <v>0.2549242058511152</v>
+        <v>0.2674469756480754</v>
       </c>
       <c r="AJ2">
-        <v>0.01004868351362921</v>
+        <v>0.02784548796609862</v>
       </c>
       <c r="AK2">
-        <v>0.01763152032080456</v>
+        <v>0.07616254879039447</v>
       </c>
       <c r="AL2">
-        <v>190.1</v>
+        <v>128.5</v>
       </c>
       <c r="AM2">
-        <v>190.1</v>
+        <v>128.5</v>
       </c>
       <c r="AN2">
-        <v>4.277093795561315</v>
+        <v>1.187430245535714</v>
       </c>
       <c r="AO2">
-        <v>5.706470278800631</v>
+        <v>21.05369649805447</v>
       </c>
       <c r="AP2">
-        <v>0.2243641665316702</v>
+        <v>0.2681361607142856</v>
       </c>
       <c r="AQ2">
-        <v>5.706470278800631</v>
+        <v>21.05369649805447</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.144</v>
+        <v>0.059</v>
       </c>
       <c r="E3">
-        <v>-0.142</v>
+        <v>-0.011</v>
       </c>
       <c r="F3">
-        <v>1.221</v>
+        <v>-0.136</v>
       </c>
       <c r="G3">
-        <v>0.01707948725368211</v>
+        <v>0.3609605769331558</v>
       </c>
       <c r="H3">
-        <v>0.01707948725368211</v>
+        <v>0.3609605769331558</v>
       </c>
       <c r="I3">
-        <v>0.07847449289620648</v>
+        <v>0.2835819331034266</v>
       </c>
       <c r="J3">
-        <v>0.05390661720818591</v>
+        <v>0.2447875084196423</v>
       </c>
       <c r="K3">
-        <v>831</v>
+        <v>2176.9</v>
       </c>
       <c r="L3">
-        <v>0.06011458664891924</v>
+        <v>0.2281841909413947</v>
       </c>
       <c r="M3">
-        <v>1094.1</v>
+        <v>3561.5</v>
       </c>
       <c r="N3">
-        <v>0.04009337163964703</v>
+        <v>0.13269028005976</v>
       </c>
       <c r="O3">
-        <v>1.316606498194946</v>
+        <v>1.636042078184574</v>
       </c>
       <c r="P3">
-        <v>1094.1</v>
+        <v>2143.6</v>
       </c>
       <c r="Q3">
-        <v>0.04009337163964703</v>
+        <v>0.07986378894738214</v>
       </c>
       <c r="R3">
-        <v>1.316606498194946</v>
+        <v>0.9847030180531948</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1417.9</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.3981187701811035</v>
       </c>
       <c r="U3">
-        <v>5003.5</v>
+        <v>2635.8</v>
       </c>
       <c r="V3">
-        <v>0.1833536102723462</v>
+        <v>0.09820161173143771</v>
       </c>
       <c r="W3">
-        <v>0.06048563193291991</v>
+        <v>0.1508865076174501</v>
       </c>
       <c r="X3">
-        <v>0.05151743282074887</v>
+        <v>0.08331591340791074</v>
       </c>
       <c r="Y3">
-        <v>0.008968199112171039</v>
+        <v>0.06757059420953941</v>
       </c>
       <c r="Z3">
-        <v>0.7481072188157875</v>
+        <v>0.6487921982535839</v>
       </c>
       <c r="AA3">
-        <v>0.04032792947538323</v>
+        <v>0.1588162256925974</v>
       </c>
       <c r="AB3">
-        <v>0.04703746789792786</v>
+        <v>0.07915047207117519</v>
       </c>
       <c r="AC3">
-        <v>-0.006709538422544625</v>
+        <v>0.07966575362142224</v>
       </c>
       <c r="AD3">
-        <v>5280.5</v>
+        <v>3404.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5280.5</v>
+        <v>3404.6</v>
       </c>
       <c r="AG3">
-        <v>277</v>
+        <v>768.7999999999997</v>
       </c>
       <c r="AH3">
-        <v>0.1621312094518458</v>
+        <v>0.1125662499628041</v>
       </c>
       <c r="AI3">
-        <v>0.2549242058511152</v>
+        <v>0.2674469756480754</v>
       </c>
       <c r="AJ3">
-        <v>0.01004868351362921</v>
+        <v>0.02784548796609862</v>
       </c>
       <c r="AK3">
-        <v>0.01763152032080456</v>
+        <v>0.07616254879039447</v>
       </c>
       <c r="AL3">
-        <v>190.1</v>
+        <v>128.5</v>
       </c>
       <c r="AM3">
-        <v>190.1</v>
+        <v>128.5</v>
       </c>
       <c r="AN3">
-        <v>4.277093795561315</v>
+        <v>1.187430245535714</v>
       </c>
       <c r="AO3">
-        <v>5.706470278800631</v>
+        <v>21.05369649805447</v>
       </c>
       <c r="AP3">
-        <v>0.2243641665316702</v>
+        <v>0.2681361607142856</v>
       </c>
       <c r="AQ3">
-        <v>5.706470278800631</v>
+        <v>21.05369649805447</v>
       </c>
     </row>
   </sheetData>
